--- a/Documentation/IEEE Embedded Compitions.xlsx
+++ b/Documentation/IEEE Embedded Compitions.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work1\paid course\IEEE\Embedded CUSB\IEEE_CUSB26_Embedded\Documentation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48A99B8-8C33-4CC9-BB61-01FD8B57273E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Competetion</t>
   </si>
@@ -49,148 +40,351 @@
     <t>https://sac.ieee.org.eg/espc</t>
   </si>
   <si>
-    <t>ESPC is the Egyptian version of the IEEE Student Paper Contest organized by IEEE AAST Alexandria Student Branch. It gathers IEEE Student Branches from across Egypt to compete in research and technical paper writing. Participants submit a scientific paper which is evaluated by IEEE professional and senior members before the event. The contest also includes workshops about research methods, IEEE Xplore, and academic paper writing.</t>
+    <t>The Egyptian Student Paper Contest (ESPC) is the national version of the IEEE Student Paper Contest, organized annually by IEEE student branches in Egypt. The competition aims to promote scientific research, technical writing, and innovation among undergraduate students. Teams or individuals submit a scientific or engineering paper presenting a novel solution, practical system, or research contribution in any engineering field. Submitted papers are evaluated by IEEE professional members, professors, and industry experts based on originality, methodology, technical depth, implementation quality, and presentation. The event also includes workshops about research skills, IEEE Xplore, academic writing, and networking with students and experts from universities across Egypt.</t>
   </si>
   <si>
     <t>AquaVision</t>
   </si>
   <si>
+    <t>AVR students can participate by developing a small but well-designed embedded system using ATmega32 or any AVR microcontroller that solves a real engineering or community problem. The project should follow a scientific methodology: define the problem, propose a hypothesis or solution, design the system, implement the prototype, test performance, and present results with conclusions.</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype or simulation.
+2. Scientific paper in IEEE format (2–4 pages).
+3. Problem statement and objective.
+4. Hardware block diagram and software flowchart.
+5. Experimental setup and measured results (tables/graphs).
+6. Final presentation slides.
+7. GitHub repository with code and documentation.'</t>
+  </si>
+  <si>
     <t>IEEE Duino</t>
   </si>
   <si>
-    <t>SSCS</t>
-  </si>
-  <si>
-    <t>Our AVR Version</t>
-  </si>
-  <si>
-    <t>Deliverable</t>
+    <t>https://ieeeduino.org/</t>
+  </si>
+  <si>
+    <t>IEEE Duino is an international IEEE hardware competition that encourages students to transform innovative ideas into practical embedded systems using Arduino-compatible platforms. The competition is typically divided into two phases: a Design Stage, where teams submit a complete engineering proposal including the project idea, background, design criteria, block diagrams, circuit design, implementation plan, estimated cost, and development timeline; and a Build Stage, where selected teams implement the project, validate its functionality, and submit a demonstration video.</t>
+  </si>
+  <si>
+    <t>2024-2023</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing the same style of project using an ATmega32 or any AVR microcontroller instead of relying on Arduino libraries. Teams should follow the same engineering workflow as IEEE Duino: identify a real-world problem, propose an embedded solution, design the hardware and software architecture, prepare the engineering documentation, then build and demonstrate the final prototype.</t>
+  </si>
+  <si>
+    <t>Design Stage:
+1. Project title and team information.
+2. Problem statement and objectives.
+3. Project scope and background.
+4. Block diagram and system architecture.
+5. Circuit schematic and subsystem descriptions.
+6. Estimated Bill of Materials (BOM).
+7. Software flowchart or pseudocode.
+8. Development timeline.
+9. GitHub repository.
+Build Stage:
+1. Fully functional AVR prototype.
+2. Demonstration video explaining the project and its operation.</t>
+  </si>
+  <si>
+    <t>IEEE SSCS</t>
+  </si>
+  <si>
+    <t>https://arduino-contest.sscs.ieee.org/</t>
+  </si>
+  <si>
+    <t>The IEEE Solid-State Circuits Society (SSCS) Arduino Contest is an annual international competition that encourages high school and undergraduate students to design and build an embedded system addressing a yearly theme. The contest aims to introduce students to electronics through hands-on design, creativity, and innovation while promoting practical engineering skills.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing a complete embedded system using ATmega32 or any AVR microcontroller while following the same yearly challenge announced by the contest. Instead of relying on Arduino libraries</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype.
+2. Demonstration video (≈3 minutes) introducing the team, explaining the project, demonstrating the prototype, and discussing one engineering challenge and how it was solved.
+3. Hardware block diagram and circuit schematic.
+4. Source code with GitHub repository.</t>
   </si>
   <si>
     <t>EISTF</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ieee-aast.org/espc</t>
-    </r>
-  </si>
-  <si>
-    <t>Top research papers are selected and awarded during the closing ceremony after review by IEEE professionals and professors.</t>
-  </si>
-  <si>
-    <t>Winners vary yearly from different Egyptian IEEE Student Branches depending on submitted research papers.</t>
-  </si>
-  <si>
-    <t>AVR Embedded System Experimental Study: Students design a small embedded system using an AVR microcontroller (ATmega32) to study a specific engineering problem. The work follows a simplified scientific method including: system design, block diagram, implementation, testing, and results analysis. Example topics may include sensor accuracy comparison, PWM motor control efficiency, or timer-based system performance.</t>
-  </si>
-  <si>
-    <t>1️⃣ Working AVR prototype 2️⃣ Block diagram &amp; system architecture 3️⃣ Experimental setup and test results 4️⃣ IEEE-format technical paper (4–6 pages) 5️⃣ GitHub repository with code</t>
-  </si>
-  <si>
-    <t>Nile University</t>
+    <t>https://eistf.eg-ase.org/</t>
+  </si>
+  <si>
+    <t>The Egypt International Science and Technology Fair (EISTF) is one of the largest annual science and engineering competitions in Egypt, organized by the Egyptian Association for Science and Engineering (EASE). It brings together high school and university students from Egypt and other countries to present innovative scientific research and engineering projects across multiple categories such as Engineering, Environmental Engineering, Energy, Biology, Mathematics, and Computer Science.</t>
+  </si>
+  <si>
+    <t>AVR students can participate by developing an embedded system using an ATmega32 or any AVR microcontroller that addresses a real-world engineering challenge. The project should demonstrate a complete engineering workflow including problem identification, proposed solution, hardware and software design, implementation, testing, validation, and discussion of the results.</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype or Proteus simulation.
+2. Engineering project report or research paper.
+3. Problem statement and project objectives.
+4. Hardware block diagram and circuit schematic.
+5. Software flowchart or algorithm.
+6. Testing methodology and experimental results.
+7. Final presentation or poster.
+8. GitHub repository containing source code and documentation.</t>
+  </si>
+  <si>
+    <t>UGRF Nile University</t>
+  </si>
+  <si>
+    <t>https://ugrf.nu.edu.eg/</t>
+  </si>
+  <si>
+    <t>The Undergraduate Research Forum (UGRF) is a semi-annual research and innovation competition organized by Nile University. It provides undergraduate students with a platform to transform course projects, graduation projects, and innovative ideas into practical research outcomes. Students from universities across Egypt—and in recent editions internationally—present their work through research summaries, posters, prototypes, applications, videos, and presentations. Projects are evaluated by university professors, researchers, and industry experts based on originality, innovation, technical implementation, scientific methodology, presentation quality, and societal impact.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing a complete embedded system using an ATmega32 or any AVR microcontroller that addresses a real engineering or community problem. The project should demonstrate a complete engineering workflow including problem identification, system requirements, hardware and software design, implementation, testing, validation, and discussion of the results.</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype or Proteus simulation.
+2. Two-page project summary (or research paper if applicable).
+3. Project poster or presentation slides.
+4. Hardware block diagram and circuit schematic.
+5. Software flowchart or system architecture.
+6. Demonstration video (if required).
+7. Testing methodology and experimental results.
+8. GitHub repository containing source code and documentation.</t>
   </si>
   <si>
     <t>Made In Egypt</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/madeinegyptcompetition/posts/?feedView=all</t>
+  </si>
+  <si>
+    <t>Made In Egypt (MIE) is one of Egypt's largest engineering innovation competitions, organized by IEEE Egypt Young Professionals. Since 2006, it has provided a platform for senior engineering students to transform their graduation projects into products that meet real industrial and market needs. The competition bridges the gap between academia and industry by combining engineering design with entrepreneurship, business development, sustainability, and commercialization.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing a complete AVR-based embedded product that solves a real problem and demonstrates both technical excellence and product potential. Beyond building a working prototype, students should think like product engineers by defining the target users, explaining the project's value, estimating development cost, and discussing how the system could be improved or commercialized</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype.
+2. Problem statement and proposed solution.
+3. Hardware block diagram and circuit schematic.
+4. Software architecture or flowchart.
+5. Bill of Materials (BOM) and estimated cost.
+6. Testing and validation results.
+7. Product presentation (slides or poster).
+8. Demonstration video.
+9. GitHub repository with source code and documentation</t>
+  </si>
+  <si>
     <t>British Council Robotics Competition (Egypt)</t>
   </si>
   <si>
+    <t>https://www.britishcouncil.org.eg/en/exam/igcse-school/engagement-programmes/robotics-competition</t>
+  </si>
+  <si>
+    <t>The British Council Robotics Competition is an annual competition that challenges student teams to design, build, and program an autonomous racing robot capable of navigating a track containing straight paths, curves, and ramps without human intervention. Throughout the competition, participants progress through several stages including registration, training workshops, video assessment, masterclasses, and a final on-site competition. The competition aims to develop robotics, programming, engineering design, teamwork, communication, and problem-solving skills while encouraging students to apply STEM concepts in a practical and creative way.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by designing an autonomous mobile robot controlled by an ATmega32 or any AVR microcontroller. The robot should be capable of following a predefined path or navigating a simple racing track using sensors such as IR line sensors, ultrasonic sensors, or encoders. Students should apply embedded systems concepts including sensor interfacing, motor control using PWM, interrupt-driven control, timers, and real-time decision making.</t>
+  </si>
+  <si>
+    <t>1. Working autonomous AVR-based robot.
+2. Robot chassis, motor driver, sensors, and control electronics.
+3. Hardware block diagram and circuit schematic.
+4. Control algorithm / flowchart.
+5. Demonstration video showing autonomous navigation.
+6. Testing results (lap time, obstacle avoidance accuracy, line-following accuracy, etc.).
+7. Presentation slides.
+8. GitHub repository containing source code and documentation.</t>
+  </si>
+  <si>
     <t>Open Robotics Competition Egypt (ORCE)</t>
   </si>
   <si>
     <t>https://www.pua.edu.eg/open-robotics-competition-egypt-orce/</t>
   </si>
   <si>
+    <t>The Open Robotics Competition Egypt (ORCE) is one of Egypt's largest university robotics competitions, organized in collaboration with the Arab Robotics Society and hosted by Pharos University in Alexandria (PUA). The competition provides a platform for university students to showcase their engineering, robotics, and innovation skills through autonomous robots, robotic systems, and innovative engineering solutions</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by designing and implementing an autonomous robot or robotic subsystem using an ATmega32 or any AVR microcontroller. Depending on the selected category, the robot may perform line following, obstacle avoidance, object detection, robotic arm control, autonomous navigation, or another engineering task</t>
+  </si>
+  <si>
+    <t>1. Working AVR-based robotic system.
+2. Mechanical design (if applicable).
+3. Hardware block diagram and circuit schematic.
+4. Software architecture or control flowchart.
+5. Demonstration video showing task completion.
+6. Performance evaluation (accuracy, completion time, reliability, etc.).
+7. Final presentation slides.
+8. GitHub repository with source code and documentation.</t>
+  </si>
+  <si>
     <t>Robotics for Good Youth Challenge</t>
   </si>
   <si>
     <t>https://aiforgood.itu.int/robotics-for-good-youth-challenge/</t>
   </si>
   <si>
+    <t>The Robotics for Good Youth Challenge is the leading United Nations (ITU) educational robotics championship that encourages young innovators to develop autonomous robotic solutions addressing real-world global challenges. Every season introduces a new theme (such as food security or health emergencies), where teams design, build, and program a robot to complete missions on a competition field.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by designing and programming an autonomous robot using an ATmega32 or any AVR microcontroller to accomplish the year's challenge. The robot should integrate sensors, actuators, and decision-making algorithms to navigate the competition field and complete the required missions autonomously</t>
+  </si>
+  <si>
+    <t>1. Fully functional autonomous AVR-based robot.
+2. Mechanical design and robot assembly.
+3. Hardware block diagram and circuit schematic.
+4. Software architecture and control algorithm/flowchart.
+5. Demonstration video showing the robot completing the challenge missions.
+6. Performance evaluation (score, completion time, accuracy, reliability, etc.).
+7. Presentation slides explaining the design and strategy.
+8. GitHub repository containing source code and documentation.</t>
+  </si>
+  <si>
     <t>World Robot Olympiad</t>
   </si>
   <si>
     <t>https://wro-association.org/</t>
   </si>
   <si>
+    <t>The World Robot Olympiad (WRO) is one of the world's largest international robotics competitions, held annually for students aged 8–22. Organized by the WRO Association, the competition aims to develop creativity, engineering thinking, teamwork, and problem-solving through robotics. WRO offers four main categories: RoboMission, RoboSports, Future Innovators, and Future Engineers, each focusing on different aspects of robotics and engineering.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing an innovative robotic or embedded system using an ATmega32 or any AVR microcontroller, following the Future Innovators engineering workflow. The project should solve a real-world problem through robotics, sensing, automation, or intelligent control while demonstrating a structured engineering design process including problem definition, system requirements, hardware and software design, implementation, testing, and validation</t>
+  </si>
+  <si>
+    <t>1. Working AVR-based robot or embedded prototype.
+2. Problem statement and project objectives.
+3. Hardware block diagram and circuit schematic.
+4. Mechanical design (if applicable).
+5. Software architecture and control algorithm.
+6. Demonstration video showing project functionality.
+7. Testing and performance evaluation.
+8. Presentation slides or project poster.
+9. GitHub repository with source code and documentation.</t>
+  </si>
+  <si>
     <t>Imagine Cup</t>
   </si>
   <si>
     <t>https://imaginecup.microsoft.com/en-us</t>
   </si>
   <si>
+    <t>Imagine Cup is Microsoft's global student technology and startup competition. It encourages students to transform innovative ideas into market-ready technology startups that solve real-world problems. Teams develop a Minimum Viable Product (MVP), validate it with potential users, and present both the technical and business aspects of their solution.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing an AVR-based embedded product that addresses a real-world problem while following a startup development process. Instead of focusing only on the hardware, students should identify target users, define the value proposition, design and implement a functional MVP using an ATmega32 or any AVR microcontroller, test the solution with potential users, and demonstrate how the product could evolve into a commercial solution</t>
+  </si>
+  <si>
+    <t>1. Functional AVR-based MVP (prototype).
+2. Problem statement and customer needs analysis.
+3. Hardware block diagram and circuit schematic.
+4. Software architecture and system flowchart.
+5. Bill of Materials (BOM) and estimated development cost.
+6. Testing and user validation results.
+7. Pitch Deck (10–15 slides).
+8. 3-minute Pitch Video.
+9. Demonstration Video (2–3 minutes).
+10. GitHub repository containing source code and documentation.</t>
+  </si>
+  <si>
     <t>Hackster.io Hardware Contests</t>
   </si>
   <si>
     <t>https://www.hackster.io/contests</t>
   </si>
   <si>
+    <t>Hackster.io is one of the world's largest hardware development communities and regularly hosts international hardware competitions in collaboration with leading technology companies such as Arduino, Microchip, STMicroelectronics, NXP, Qualcomm, Edge Impulse, and many others. Unlike a single recurring competition, Hackster provides multiple themed contests throughout the year covering embedded systems, IoT, robotics, AI, edge computing, wearables, automotive, smart home, and industrial automation.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing a complete embedded project using an ATmega32 or any AVR microcontroller that addresses the current contest theme. The project should follow professional engineering practices, including problem definition, hardware and software design, implementation, testing, and complete online documentation</t>
+  </si>
+  <si>
+    <t>1. Working AVR prototype.
+2. Complete Hackster project page documenting the build process.
+3. Project description and objectives.
+4. Hardware block diagram and circuit schematic.
+5. Bill of Materials (BOM).
+6. Source code with GitHub repository.
+7. Build instructions and project photos.
+8. Demonstration video showing the project in operation.
+9. Testing results and performance evaluation.</t>
+  </si>
+  <si>
     <t>ST Innovation Challenge</t>
   </si>
   <si>
     <t>https://www.innovationworldcup.com/categories/st-innovation-challenge/</t>
   </si>
   <si>
+    <t>The ST Innovation Challenge, powered by STMicroelectronics, is a flagship competition within the Innovation World Cup® Series that supports startups and innovators developing intelligent embedded systems. The challenge focuses on creating context-aware electronic solutions by combining sensing, embedded processing, connectivity, and Edge AI to solve real industrial and consumer problems.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by developing an embedded system using an ATmega32 or any AVR microcontroller that solves a real industrial or consumer problem. Although the official competition encourages the use of ST hardware and Edge AI technologies, the workshop version focuses on following the same engineering and product development methodology. Students should identify a real problem, propose an innovative solution, design the complete hardware and software architecture, implement a functional prototype, validate its performance, and demonstrate its potential as a market-ready product</t>
+  </si>
+  <si>
+    <t>1. Functional AVR-based prototype.
+2. Problem statement and value proposition.
+3. Hardware block diagram and circuit schematic.
+4. Software architecture and flowchart.
+5. Bill of Materials (BOM) and estimated production cost.
+6. Testing and validation results.
+7. Product presentation (Pitch Deck).
+8. Demonstration video.
+9. GitHub repository with source code and documentation.</t>
+  </si>
+  <si>
     <t>NXP Cup</t>
   </si>
   <si>
     <t>https://nxpcup.nxp.com/</t>
+  </si>
+  <si>
+    <t>The NXP Cup is a global autonomous vehicle competition organized by NXP Semiconductors. Student teams design, build, and program an autonomous model car capable of navigating a race track at high speed without human intervention. The competition emphasizes embedded systems, real-time programming, control systems, sensing, autonomous navigation, and teamwork.</t>
+  </si>
+  <si>
+    <t>AVR workshop students can participate by designing and implementing an autonomous AVR-based vehicle using an ATmega32 or any AVR microcontroller. Instead of using the official NXP development boards, students should build a simplified self-driving car capable of line following and autonomous navigation using sensors, motor drivers, PWM, timers, interrupts, and real-time control algorithms.</t>
+  </si>
+  <si>
+    <t>1. Fully functional AVR autonomous vehicle.
+2. Chassis, steering and motor control system.
+3. Sensor integration (IR line sensors, encoders, ultrasonic, camera if applicable).
+4. Hardware block diagram and circuit schematic.
+5. Software architecture and control algorithm (Flowchart/Pseudocode).
+6. Vehicle tuning and control strategy documentation (PID or equivalent if used).
+7. Performance evaluation (lap time, tracking accuracy, stability, obstacle handling if applicable).
+8. Demonstration video of the autonomous vehicle completing the track.
+9. Presentation slides.
+10. GitHub repository containing source code and documentation.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -198,61 +392,47 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+  <cellXfs count="7">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -260,7 +440,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -450,26 +630,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="35.109375" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="121.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="35.13"/>
+    <col customWidth="1" min="2" max="2" width="40.38"/>
+    <col customWidth="1" min="3" max="3" width="121.38"/>
+    <col customWidth="1" min="6" max="6" width="66.5"/>
+    <col customWidth="1" min="7" max="7" width="48.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="68.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -503,227 +681,293 @@
         <v>9</v>
       </c>
       <c r="D2" s="3">
-        <v>2025</v>
+        <v>2025.0</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="K4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="K5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="8"/>
+        <v>70</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://www.facebook.com/share/p/1BuUu7kevq/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="D2"/>
+    <hyperlink r:id="rId3" ref="E2"/>
+    <hyperlink r:id="rId4" ref="B3"/>
+    <hyperlink r:id="rId5" ref="B4"/>
+    <hyperlink r:id="rId6" ref="B5"/>
+    <hyperlink r:id="rId7" ref="B6"/>
+    <hyperlink r:id="rId8" ref="B7"/>
+    <hyperlink r:id="rId9" ref="B8"/>
+    <hyperlink r:id="rId10" ref="B9"/>
+    <hyperlink r:id="rId11" ref="B10"/>
+    <hyperlink r:id="rId12" ref="B11"/>
+    <hyperlink r:id="rId13" ref="B12"/>
+    <hyperlink r:id="rId14" ref="B13"/>
+    <hyperlink r:id="rId15" ref="B14"/>
+    <hyperlink r:id="rId16" ref="B15"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>